--- a/data/trans_orig/P5706-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P5706-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas en 2007</t>
+          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>460699</t>
+          <t>455341</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>523533</t>
+          <t>519622</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>558827</t>
+          <t>559002</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>632324</t>
+          <t>628585</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1033467</t>
+          <t>1035166</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1130145</t>
+          <t>1130691</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,18%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>270892</t>
+          <t>270573</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>329018</t>
+          <t>328514</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>347872</t>
+          <t>351180</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>416060</t>
+          <t>412760</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>641956</t>
+          <t>635526</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>726227</t>
+          <t>724650</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,88%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>148826</t>
+          <t>148969</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>195524</t>
+          <t>197391</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>217236</t>
+          <t>215788</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>272245</t>
+          <t>270940</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>380895</t>
+          <t>379341</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>453558</t>
+          <t>454556</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,37%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44641</t>
+          <t>44014</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73580</t>
+          <t>75870</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59034</t>
+          <t>59095</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>91487</t>
+          <t>91162</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>111340</t>
+          <t>111303</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>155073</t>
+          <t>156760</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5757</t>
+          <t>5458</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19279</t>
+          <t>19503</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14833</t>
+          <t>15365</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35199</t>
+          <t>35085</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>23727</t>
+          <t>24624</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>47837</t>
+          <t>49080</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>969413</t>
+          <t>973858</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1051609</t>
+          <t>1049574</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>884659</t>
+          <t>887108</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>960068</t>
+          <t>966206</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1875198</t>
+          <t>1882232</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1988001</t>
+          <t>1989244</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,63%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>434103</t>
+          <t>438668</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>509171</t>
+          <t>509745</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>414699</t>
+          <t>410675</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>483159</t>
+          <t>481721</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>875171</t>
+          <t>871187</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>978690</t>
+          <t>970304</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,57%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>140580</t>
+          <t>141931</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>191247</t>
+          <t>188668</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>141262</t>
+          <t>141622</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>191095</t>
+          <t>188373</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>295012</t>
+          <t>293838</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>364274</t>
+          <t>361536</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22618</t>
+          <t>22571</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46054</t>
+          <t>44697</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31545</t>
+          <t>32522</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60548</t>
+          <t>62927</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>60212</t>
+          <t>62238</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>96080</t>
+          <t>97491</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5820</t>
+          <t>5941</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21022</t>
+          <t>20581</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,82 +1882,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>7810</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>3134</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>15217</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>19257</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>11227</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>29475</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>7810</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>3235</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>16932</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>19257</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>11991</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>31259</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>314112</t>
+          <t>312154</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>358915</t>
+          <t>358877</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>267139</t>
+          <t>267556</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>312289</t>
+          <t>310761</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>592321</t>
+          <t>595132</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>657504</t>
+          <t>660405</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>64,25%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>131405</t>
+          <t>130491</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>174302</t>
+          <t>174314</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>110419</t>
+          <t>113481</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>152731</t>
+          <t>151277</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>252969</t>
+          <t>253462</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>313373</t>
+          <t>312873</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,44%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>35105</t>
+          <t>33907</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>62213</t>
+          <t>62836</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27477</t>
+          <t>27146</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>52133</t>
+          <t>51582</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>68804</t>
+          <t>68986</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>104916</t>
+          <t>107010</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7130</t>
+          <t>7279</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23918</t>
+          <t>22718</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9996</t>
+          <t>10042</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26501</t>
+          <t>26213</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20517</t>
+          <t>19409</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>43432</t>
+          <t>43658</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8386</t>
+          <t>9450</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4804</t>
+          <t>4663</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>942</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10342</t>
+          <t>10061</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1777862</t>
+          <t>1776454</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1890915</t>
+          <t>1895185</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1739176</t>
+          <t>1743636</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1862430</t>
+          <t>1861644</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3555446</t>
+          <t>3563453</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3723568</t>
+          <t>3726710</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>55,99%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>877421</t>
+          <t>876951</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>976983</t>
+          <t>976673</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>913740</t>
+          <t>910956</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1023439</t>
+          <t>1011572</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1811057</t>
+          <t>1811073</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1956495</t>
+          <t>1961557</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>348849</t>
+          <t>347860</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>420049</t>
+          <t>424308</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>405253</t>
+          <t>404015</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>484785</t>
+          <t>482633</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>770961</t>
+          <t>773725</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>883640</t>
+          <t>881920</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>85972</t>
+          <t>84997</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>126603</t>
+          <t>126524</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>112603</t>
+          <t>111628</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>159073</t>
+          <t>160847</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>208347</t>
+          <t>208435</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>271662</t>
+          <t>266794</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>17101</t>
+          <t>15814</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>41501</t>
+          <t>37162</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>22174</t>
+          <t>22476</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>45589</t>
+          <t>45136</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,47 +3281,47 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>57725</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>43829</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>75316</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>0,66%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>57725</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>43424</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>75685</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas en 2012</t>
+          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas en 2012 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>492331</t>
+          <t>492272</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>553419</t>
+          <t>554325</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>640199</t>
+          <t>639376</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>712783</t>
+          <t>716273</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1155117</t>
+          <t>1148386</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1251790</t>
+          <t>1247651</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>54,1%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>251998</t>
+          <t>252271</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>309478</t>
+          <t>309745</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>409716</t>
+          <t>408523</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>481781</t>
+          <t>479133</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>680202</t>
+          <t>681454</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>767067</t>
+          <t>768786</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,33%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>107872</t>
+          <t>109270</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>150976</t>
+          <t>152294</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>139168</t>
+          <t>136509</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>186934</t>
+          <t>186063</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>260572</t>
+          <t>261412</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>325620</t>
+          <t>325684</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16628</t>
+          <t>16810</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37970</t>
+          <t>35319</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27028</t>
+          <t>26988</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53962</t>
+          <t>53801</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48567</t>
+          <t>49290</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>80248</t>
+          <t>82467</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5165</t>
+          <t>5074</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19864</t>
+          <t>18975</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7996</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23851</t>
+          <t>23757</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15251</t>
+          <t>15498</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>36153</t>
+          <t>36432</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1166932</t>
+          <t>1159974</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1253984</t>
+          <t>1248604</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>981561</t>
+          <t>982005</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1067868</t>
+          <t>1067326</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>60,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2165811</t>
+          <t>2173464</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2296543</t>
+          <t>2291564</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>61,66%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>505699</t>
+          <t>509975</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>584540</t>
+          <t>591482</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>483766</t>
+          <t>485711</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>564613</t>
+          <t>563129</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1016460</t>
+          <t>1018589</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1128819</t>
+          <t>1129805</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,4%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>142650</t>
+          <t>140625</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>191066</t>
+          <t>190195</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>130655</t>
+          <t>130210</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>182832</t>
+          <t>178989</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>285521</t>
+          <t>286396</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>354810</t>
+          <t>354237</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21014</t>
+          <t>20038</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43823</t>
+          <t>45003</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25287</t>
+          <t>25622</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52124</t>
+          <t>53100</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51853</t>
+          <t>50537</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>88147</t>
+          <t>85666</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19555</t>
+          <t>20823</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8062</t>
+          <t>7794</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26769</t>
+          <t>26166</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15019</t>
+          <t>15388</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>38429</t>
+          <t>37758</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>304038</t>
+          <t>302873</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>348482</t>
+          <t>348109</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>285963</t>
+          <t>287947</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>329865</t>
+          <t>328874</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>602599</t>
+          <t>602841</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>664145</t>
+          <t>662774</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>70,68%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>85785</t>
+          <t>84791</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>123581</t>
+          <t>123151</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>88729</t>
+          <t>86941</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>128067</t>
+          <t>125100</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>183181</t>
+          <t>185745</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>239008</t>
+          <t>238663</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25318</t>
+          <t>23831</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>51777</t>
+          <t>49018</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25420</t>
+          <t>24735</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>49606</t>
+          <t>48430</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>54635</t>
+          <t>56405</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>91510</t>
+          <t>91162</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5570</t>
+          <t>6253</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21656</t>
+          <t>22914</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3832</t>
+          <t>3789</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14736</t>
+          <t>14493</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11737</t>
+          <t>11513</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31514</t>
+          <t>31835</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12265</t>
+          <t>10979</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,62 +5543,62 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>2186</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2132</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>12081</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>2186</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>12356</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1994790</t>
+          <t>1996417</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2111035</t>
+          <t>2111286</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1948080</t>
+          <t>1951364</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2068375</t>
+          <t>2071652</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3981276</t>
+          <t>3975755</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4153886</t>
+          <t>4154017</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>881227</t>
+          <t>879412</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>988206</t>
+          <t>988552</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1023986</t>
+          <t>1018911</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1128698</t>
+          <t>1132403</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1937399</t>
+          <t>1926063</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2089554</t>
+          <t>2083511</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,93%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>296960</t>
+          <t>298971</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>369705</t>
+          <t>367561</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>316180</t>
+          <t>318529</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>386991</t>
+          <t>388878</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>629008</t>
+          <t>632322</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>732538</t>
+          <t>733730</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>51159</t>
+          <t>51864</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>85963</t>
+          <t>86643</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>67029</t>
+          <t>66009</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>103725</t>
+          <t>103961</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>127003</t>
+          <t>126254</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>178506</t>
+          <t>179501</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14225</t>
+          <t>13171</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>35853</t>
+          <t>36561</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>19693</t>
+          <t>20096</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>41884</t>
+          <t>42645</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,47 +6240,47 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>52300</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>38587</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>70903</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>0,55%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>52300</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>38557</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>70387</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas en 2016</t>
+          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas en 2016 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>300858</t>
+          <t>297138</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>353421</t>
+          <t>351314</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>368473</t>
+          <t>371028</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>435524</t>
+          <t>435518</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>682489</t>
+          <t>687380</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>772033</t>
+          <t>769453</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,03%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>223280</t>
+          <t>223693</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>274651</t>
+          <t>274670</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>312342</t>
+          <t>313791</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>374667</t>
+          <t>379768</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>553141</t>
+          <t>552111</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>633924</t>
+          <t>632605</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,2%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>123633</t>
+          <t>127615</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>169232</t>
+          <t>169629</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>166375</t>
+          <t>166570</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>219229</t>
+          <t>219913</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>306666</t>
+          <t>305334</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>373108</t>
+          <t>369630</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,15%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20336</t>
+          <t>20600</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42000</t>
+          <t>42795</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31994</t>
+          <t>31739</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>59471</t>
+          <t>62153</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58321</t>
+          <t>57900</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>94593</t>
+          <t>95969</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>962</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9456</t>
+          <t>9833</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5014</t>
+          <t>5392</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19983</t>
+          <t>21212</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,47 +7153,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>15300</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>8682</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>25302</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>0,5%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>15300</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>8529</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>25093</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>965640</t>
+          <t>966335</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1064258</t>
+          <t>1063981</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>923221</t>
+          <t>922527</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1012485</t>
+          <t>1012580</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1921207</t>
+          <t>1914391</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2048614</t>
+          <t>2041313</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,32%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>698363</t>
+          <t>690632</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>784911</t>
+          <t>779630</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>661288</t>
+          <t>662736</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>750424</t>
+          <t>749953</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1380262</t>
+          <t>1384168</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1502888</t>
+          <t>1497694</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>36,92%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>238631</t>
+          <t>236076</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>300041</t>
+          <t>299170</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>241314</t>
+          <t>237360</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>302099</t>
+          <t>302635</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>495471</t>
+          <t>497328</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>582172</t>
+          <t>581604</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,34%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28976</t>
+          <t>29946</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56362</t>
+          <t>58412</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25276</t>
+          <t>25107</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48743</t>
+          <t>50605</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>59017</t>
+          <t>60677</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>96905</t>
+          <t>97111</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6300</t>
+          <t>6479</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20202</t>
+          <t>20656</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,82 +7800,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>7320</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2930</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>13540</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>19515</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>12291</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>30164</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>0,3%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>7320</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>3172</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>13753</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>19515</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>12491</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>30721</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>291202</t>
+          <t>292282</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>339149</t>
+          <t>340311</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>320115</t>
+          <t>319701</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>366010</t>
+          <t>365759</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>624551</t>
+          <t>625055</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>690853</t>
+          <t>693513</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,38%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>151157</t>
+          <t>152017</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>194457</t>
+          <t>197656</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>135079</t>
+          <t>136066</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>177385</t>
+          <t>178371</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>296464</t>
+          <t>298271</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>359012</t>
+          <t>359188</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,83%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>40877</t>
+          <t>39628</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>70589</t>
+          <t>69959</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>29956</t>
+          <t>30265</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>55612</t>
+          <t>55293</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>77089</t>
+          <t>77525</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>116338</t>
+          <t>116886</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -8359,7 +8359,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5827</t>
+          <t>4614</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>4598</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15893</t>
+          <t>16208</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>4860</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17634</t>
+          <t>17852</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7068</t>
+          <t>6753</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,62 +8502,62 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>2052</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>7230</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>2052</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>7122</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1596443</t>
+          <t>1598958</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1717622</t>
+          <t>1714262</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1655742</t>
+          <t>1648604</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1778259</t>
+          <t>1772494</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3281504</t>
+          <t>3279957</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3445713</t>
+          <t>3452672</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>50,05%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1101688</t>
+          <t>1099171</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1216821</t>
+          <t>1211791</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1142786</t>
+          <t>1144142</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1260002</t>
+          <t>1262227</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2282469</t>
+          <t>2279351</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2440245</t>
+          <t>2452819</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,56%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>427098</t>
+          <t>426280</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>509557</t>
+          <t>509524</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,7 +8938,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>463358</t>
+          <t>463313</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>548078</t>
+          <t>550939</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8978,7 +8978,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>913293</t>
+          <t>919064</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1031751</t>
+          <t>1037744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,04%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>57218</t>
+          <t>57464</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>90572</t>
+          <t>93095</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>72491</t>
+          <t>72129</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>110882</t>
+          <t>110918</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>135455</t>
+          <t>135941</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>189664</t>
+          <t>188403</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11030</t>
+          <t>10935</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>28127</t>
+          <t>28438</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10498</t>
+          <t>10879</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>29302</t>
+          <t>29559</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>25827</t>
+          <t>26006</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>49755</t>
+          <t>51360</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas en 2023</t>
+          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas en 2023 (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9610,12 +9610,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>233942</t>
+          <t>234197</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>276272</t>
+          <t>275812</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9625,12 +9625,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>313851</t>
+          <t>314451</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>359534</t>
+          <t>359174</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9680,12 +9680,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>562759</t>
+          <t>562031</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>623037</t>
+          <t>623574</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9695,12 +9695,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,48%</t>
         </is>
       </c>
     </row>
@@ -9723,12 +9723,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>115556</t>
+          <t>116399</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>153342</t>
+          <t>153418</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>209019</t>
+          <t>209831</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>247589</t>
+          <t>248115</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>336598</t>
+          <t>334349</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>389602</t>
+          <t>389852</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,94%</t>
         </is>
       </c>
     </row>
@@ -9836,12 +9836,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>62446</t>
+          <t>63117</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>90933</t>
+          <t>93045</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9851,12 +9851,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>97524</t>
+          <t>98463</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>125785</t>
+          <t>125753</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9886,7 +9886,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>168891</t>
+          <t>166888</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>212053</t>
+          <t>208900</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,58%</t>
         </is>
       </c>
     </row>
@@ -9949,12 +9949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22725</t>
+          <t>23592</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41683</t>
+          <t>42564</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9984,12 +9984,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>47944</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70937</t>
+          <t>70393</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>76381</t>
+          <t>75606</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>105510</t>
+          <t>104915</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8175</t>
+          <t>8045</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20667</t>
+          <t>20810</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9618</t>
+          <t>9906</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>20142</t>
+          <t>20686</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20413</t>
+          <t>20275</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>37216</t>
+          <t>36835</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -10292,12 +10292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1325526</t>
+          <t>1324529</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1711227</t>
+          <t>1723729</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10307,12 +10307,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>875744</t>
+          <t>913538</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1336857</t>
+          <t>1337256</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10342,12 +10342,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2303345</t>
+          <t>2313489</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2932189</t>
+          <t>2923369</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>64,64%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>433838</t>
+          <t>405205</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>713609</t>
+          <t>713471</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>656833</t>
+          <t>660910</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1207732</t>
+          <t>1187174</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1216215</t>
+          <t>1207295</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1920071</t>
+          <t>1923250</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,52%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>97390</t>
+          <t>104172</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>177214</t>
+          <t>179070</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>100511</t>
+          <t>97389</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>161018</t>
+          <t>160236</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>227316</t>
+          <t>225655</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>325831</t>
+          <t>325087</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>37387</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>73757</t>
+          <t>74137</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48552</t>
+          <t>48277</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>87063</t>
+          <t>85647</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>95712</t>
+          <t>95947</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>149783</t>
+          <t>149819</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12939</t>
+          <t>12181</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33170</t>
+          <t>33343</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11245</t>
+          <t>11115</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30910</t>
+          <t>31198</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>27472</t>
+          <t>26543</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>54669</t>
+          <t>54309</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>389070</t>
+          <t>387521</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>439118</t>
+          <t>437829</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>445483</t>
+          <t>446111</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>487045</t>
+          <t>486508</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11024,47 +11024,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>67,69%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>73,82%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>881256</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>848982</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>913349</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>67,59%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>73,9%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1099</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>881256</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>843903</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>912608</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>67,59%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>70,05%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>160419</t>
+          <t>159503</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>206691</t>
+          <t>206717</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>135416</t>
+          <t>135059</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>171077</t>
+          <t>171721</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>309307</t>
+          <t>305843</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>369754</t>
+          <t>367962</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,22%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23694</t>
+          <t>23494</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>48946</t>
+          <t>49583</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20056</t>
+          <t>20403</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40881</t>
+          <t>40288</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>48079</t>
+          <t>48410</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>80721</t>
+          <t>80624</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>5726</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17652</t>
+          <t>17437</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2468</t>
+          <t>2422</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9138</t>
+          <t>9063</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9858</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23312</t>
+          <t>23139</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -11426,12 +11426,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1103</t>
+          <t>974</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10578</t>
+          <t>10391</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2808</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10804</t>
+          <t>10693</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4822</t>
+          <t>5197</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15697</t>
+          <t>16970</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1985341</t>
+          <t>1987432</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2410875</t>
+          <t>2404777</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1579917</t>
+          <t>1613122</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2140960</t>
+          <t>2143271</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3779132</t>
+          <t>3741887</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4398924</t>
+          <t>4374408</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>61,73%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>713885</t>
+          <t>740003</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1033956</t>
+          <t>1031808</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1043822</t>
+          <t>1039282</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1732345</t>
+          <t>1726856</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1916123</t>
+          <t>1924562</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2618872</t>
+          <t>2704059</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>38,16%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>201630</t>
+          <t>194457</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>296205</t>
+          <t>294580</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>217087</t>
+          <t>222655</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>306246</t>
+          <t>306972</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>465537</t>
+          <t>466711</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>591049</t>
+          <t>590926</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11967,7 +11967,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>73454</t>
+          <t>72932</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>120255</t>
+          <t>118814</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>103994</t>
+          <t>105036</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>153312</t>
+          <t>153515</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>192266</t>
+          <t>193934</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>259855</t>
+          <t>259900</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,7 +12080,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -12108,12 +12108,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>26022</t>
+          <t>26370</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>52392</t>
+          <t>52113</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>27626</t>
+          <t>28575</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>51364</t>
+          <t>51105</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12158,12 +12158,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>61449</t>
+          <t>60930</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>94738</t>
+          <t>96370</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P5706-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P5706-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>455341</t>
+          <t>459798</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>519622</t>
+          <t>520493</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>559002</t>
+          <t>553892</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>628585</t>
+          <t>624902</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1035166</t>
+          <t>1034032</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1130691</t>
+          <t>1125124</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>47,94%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>270573</t>
+          <t>271799</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>328514</t>
+          <t>329431</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>351180</t>
+          <t>349101</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>412760</t>
+          <t>412535</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>635526</t>
+          <t>639565</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>724650</t>
+          <t>725050</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,89%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>148969</t>
+          <t>151225</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>197391</t>
+          <t>197026</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>215788</t>
+          <t>216836</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>270940</t>
+          <t>273563</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>379341</t>
+          <t>379470</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>454556</t>
+          <t>451315</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,23%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44014</t>
+          <t>44413</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75870</t>
+          <t>75368</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59095</t>
+          <t>59541</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>91162</t>
+          <t>91810</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>111303</t>
+          <t>110185</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>156760</t>
+          <t>154931</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5458</t>
+          <t>6193</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19503</t>
+          <t>22369</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15365</t>
+          <t>15369</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35085</t>
+          <t>36483</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>24624</t>
+          <t>24776</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>49080</t>
+          <t>48037</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>973858</t>
+          <t>971296</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1049574</t>
+          <t>1052821</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>887108</t>
+          <t>883237</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>966206</t>
+          <t>965679</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>60,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1882232</t>
+          <t>1876117</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1989244</t>
+          <t>1986960</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>60,56%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>438668</t>
+          <t>438230</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>509745</t>
+          <t>509993</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>410675</t>
+          <t>415223</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>481721</t>
+          <t>489267</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>871187</t>
+          <t>873267</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>970304</t>
+          <t>971967</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,62%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>141931</t>
+          <t>142600</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>188668</t>
+          <t>191010</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>141622</t>
+          <t>139420</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>188373</t>
+          <t>187844</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>293838</t>
+          <t>292240</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>361536</t>
+          <t>359758</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,96%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22571</t>
+          <t>22980</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44697</t>
+          <t>45761</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32522</t>
+          <t>32682</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62927</t>
+          <t>63134</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>62238</t>
+          <t>60286</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>97491</t>
+          <t>96483</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>5770</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20581</t>
+          <t>20819</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3134</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15217</t>
+          <t>15634</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,47 +1917,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>19257</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>11708</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>31377</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>0,96%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>19257</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>11227</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>29475</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>312154</t>
+          <t>311922</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>358877</t>
+          <t>359099</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>267556</t>
+          <t>268066</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>310761</t>
+          <t>311141</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>595132</t>
+          <t>596203</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>660405</t>
+          <t>660133</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>64,23%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>130491</t>
+          <t>132779</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>174314</t>
+          <t>174370</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>113481</t>
+          <t>111864</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>151277</t>
+          <t>151840</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>253462</t>
+          <t>253683</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>312873</t>
+          <t>309984</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,16%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>33907</t>
+          <t>34422</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>62836</t>
+          <t>63271</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27146</t>
+          <t>28535</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>51582</t>
+          <t>52822</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>68986</t>
+          <t>68933</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>107010</t>
+          <t>105739</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7279</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22718</t>
+          <t>23190</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10042</t>
+          <t>9100</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26213</t>
+          <t>25714</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19409</t>
+          <t>21301</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>43658</t>
+          <t>44517</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9450</t>
+          <t>8180</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4663</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>941</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10061</t>
+          <t>9956</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1776454</t>
+          <t>1782455</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1895185</t>
+          <t>1895660</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1743636</t>
+          <t>1753313</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1861644</t>
+          <t>1860341</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3563453</t>
+          <t>3557998</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3726710</t>
+          <t>3729954</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>56,04%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>876951</t>
+          <t>871802</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>976673</t>
+          <t>978859</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>910956</t>
+          <t>905533</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1011572</t>
+          <t>1015005</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1811073</t>
+          <t>1811345</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1961557</t>
+          <t>1956761</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,4%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>347860</t>
+          <t>348783</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>424308</t>
+          <t>422390</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>404015</t>
+          <t>407884</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>482633</t>
+          <t>486332</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>773725</t>
+          <t>770266</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>881920</t>
+          <t>886079</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>84997</t>
+          <t>84750</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>126524</t>
+          <t>124773</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>111628</t>
+          <t>113086</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>160847</t>
+          <t>160810</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>208435</t>
+          <t>207899</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>266794</t>
+          <t>269583</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>15814</t>
+          <t>16884</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>37162</t>
+          <t>38902</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>22476</t>
+          <t>21968</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>45136</t>
+          <t>44978</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>43829</t>
+          <t>42485</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>75316</t>
+          <t>74534</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>492272</t>
+          <t>491318</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>554325</t>
+          <t>557183</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>639376</t>
+          <t>640304</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>716273</t>
+          <t>713651</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1148386</t>
+          <t>1152531</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1247651</t>
+          <t>1252936</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>54,33%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>252271</t>
+          <t>252466</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>309745</t>
+          <t>308965</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>408523</t>
+          <t>412849</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>479133</t>
+          <t>481657</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>681454</t>
+          <t>683811</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>768786</t>
+          <t>775005</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,6%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>109270</t>
+          <t>108818</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>152294</t>
+          <t>151507</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136509</t>
+          <t>135927</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>186063</t>
+          <t>185940</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>261412</t>
+          <t>262287</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>325684</t>
+          <t>325214</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,1%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16810</t>
+          <t>15553</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35319</t>
+          <t>35519</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26988</t>
+          <t>28008</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53801</t>
+          <t>52503</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49290</t>
+          <t>49019</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>82467</t>
+          <t>82290</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5074</t>
+          <t>4986</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18975</t>
+          <t>19604</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>7742</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23757</t>
+          <t>23669</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15498</t>
+          <t>15325</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>36432</t>
+          <t>37613</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1159974</t>
+          <t>1157783</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1248604</t>
+          <t>1251116</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>982005</t>
+          <t>976884</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1067326</t>
+          <t>1067040</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2173464</t>
+          <t>2172388</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2291564</t>
+          <t>2299639</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>58,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,87%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>509975</t>
+          <t>505822</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>591482</t>
+          <t>587421</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>485711</t>
+          <t>487254</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>563129</t>
+          <t>567769</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1018589</t>
+          <t>1014764</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1129805</t>
+          <t>1131087</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,43%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>140625</t>
+          <t>142810</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>190195</t>
+          <t>192402</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>130210</t>
+          <t>130745</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>178989</t>
+          <t>179608</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>286396</t>
+          <t>283398</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>354237</t>
+          <t>355195</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,56%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20038</t>
+          <t>21322</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45003</t>
+          <t>44313</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,82 +4728,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>36498</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>24708</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>51366</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>67204</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>51314</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>85200</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>2,29%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>36498</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>25622</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>53100</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,08%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>67204</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>50537</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>85666</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20823</t>
+          <t>20233</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4846,77 +4846,77 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>14862</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>8114</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>25648</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>25021</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>15210</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>39278</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>1,06%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>14862</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>7794</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>26166</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>25021</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>15388</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>37758</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>302873</t>
+          <t>303840</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>348109</t>
+          <t>348997</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>287947</t>
+          <t>285889</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>328874</t>
+          <t>328098</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>602841</t>
+          <t>605163</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>662774</t>
+          <t>667707</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>71,21%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>84791</t>
+          <t>86985</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>123151</t>
+          <t>124605</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>86941</t>
+          <t>85430</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>125100</t>
+          <t>124765</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>185745</t>
+          <t>184797</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>238663</t>
+          <t>238721</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,46%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23831</t>
+          <t>25064</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>49018</t>
+          <t>51508</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24735</t>
+          <t>25144</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>48430</t>
+          <t>49561</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>56405</t>
+          <t>54545</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>91162</t>
+          <t>91090</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6253</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22914</t>
+          <t>22165</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3789</t>
+          <t>3879</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14493</t>
+          <t>15658</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11513</t>
+          <t>11206</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31835</t>
+          <t>31508</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10979</t>
+          <t>10106</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12081</t>
+          <t>10877</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1996417</t>
+          <t>1999970</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2111286</t>
+          <t>2123491</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1951364</t>
+          <t>1952273</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2071652</t>
+          <t>2071832</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3975755</t>
+          <t>3976595</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4154017</t>
+          <t>4156020</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,71%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>879412</t>
+          <t>880680</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>988552</t>
+          <t>988677</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,7 +5866,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1018911</t>
+          <t>1017475</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1132403</t>
+          <t>1124848</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1926063</t>
+          <t>1928878</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2083511</t>
+          <t>2089559</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,02%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>298971</t>
+          <t>296766</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>367561</t>
+          <t>369880</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>318529</t>
+          <t>316653</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>388878</t>
+          <t>386953</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>632322</t>
+          <t>629882</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>733730</t>
+          <t>736269</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>51864</t>
+          <t>51130</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>86643</t>
+          <t>85074</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>66009</t>
+          <t>65437</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>103961</t>
+          <t>104361</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>126254</t>
+          <t>126500</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>179501</t>
+          <t>179160</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13171</t>
+          <t>14194</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>36561</t>
+          <t>36071</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>20096</t>
+          <t>20504</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>42645</t>
+          <t>44888</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>38587</t>
+          <t>39200</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>70903</t>
+          <t>70142</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>297138</t>
+          <t>298101</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>351314</t>
+          <t>351147</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>371028</t>
+          <t>368748</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>435518</t>
+          <t>434637</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>687380</t>
+          <t>685971</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>769453</t>
+          <t>765211</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>43,78%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>223693</t>
+          <t>222661</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>274670</t>
+          <t>272042</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>313791</t>
+          <t>316840</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>379768</t>
+          <t>378703</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>552111</t>
+          <t>554331</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>632605</t>
+          <t>635661</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,37%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>127615</t>
+          <t>126803</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>169629</t>
+          <t>169214</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>166570</t>
+          <t>168796</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>219913</t>
+          <t>220959</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>305334</t>
+          <t>306684</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>369630</t>
+          <t>371318</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,25%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20600</t>
+          <t>20564</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42795</t>
+          <t>42206</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31739</t>
+          <t>31713</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62153</t>
+          <t>61387</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57900</t>
+          <t>58222</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>95969</t>
+          <t>92813</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>984</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9833</t>
+          <t>10317</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5392</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21212</t>
+          <t>20841</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8682</t>
+          <t>7747</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25302</t>
+          <t>26290</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>966335</t>
+          <t>971011</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1063981</t>
+          <t>1060598</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>922527</t>
+          <t>923374</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1012580</t>
+          <t>1006918</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1914391</t>
+          <t>1913375</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2041313</t>
+          <t>2043341</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>50,37%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>690632</t>
+          <t>694654</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>779630</t>
+          <t>782013</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>662736</t>
+          <t>663261</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>749953</t>
+          <t>748407</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1384168</t>
+          <t>1385447</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1497694</t>
+          <t>1509031</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>37,2%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>236076</t>
+          <t>237037</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>299170</t>
+          <t>302385</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>237360</t>
+          <t>243369</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>302635</t>
+          <t>304705</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>497328</t>
+          <t>492324</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>581604</t>
+          <t>579677</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,29%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29946</t>
+          <t>28630</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58412</t>
+          <t>55122</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25107</t>
+          <t>25284</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50605</t>
+          <t>49725</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>60677</t>
+          <t>61624</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>97111</t>
+          <t>97904</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6479</t>
+          <t>6666</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20656</t>
+          <t>21084</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2930</t>
+          <t>3151</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13540</t>
+          <t>15335</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12291</t>
+          <t>11801</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>30164</t>
+          <t>30029</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>292282</t>
+          <t>288374</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>340311</t>
+          <t>338498</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>319701</t>
+          <t>318360</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>365759</t>
+          <t>365713</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>625055</t>
+          <t>622796</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>693513</t>
+          <t>691972</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>63,24%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>152017</t>
+          <t>149609</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>197656</t>
+          <t>198460</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>136066</t>
+          <t>134229</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>178371</t>
+          <t>178377</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>298271</t>
+          <t>295920</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>359188</t>
+          <t>359426</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,85%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>39628</t>
+          <t>42041</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>69959</t>
+          <t>72735</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>30265</t>
+          <t>30010</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>55293</t>
+          <t>56135</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>77525</t>
+          <t>78135</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>116886</t>
+          <t>118271</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -8359,7 +8359,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4614</t>
+          <t>4997</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4598</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16208</t>
+          <t>16733</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4860</t>
+          <t>4932</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17852</t>
+          <t>17538</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6753</t>
+          <t>7216</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7230</t>
+          <t>7097</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1598958</t>
+          <t>1596183</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1714262</t>
+          <t>1710773</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1648604</t>
+          <t>1651389</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1772494</t>
+          <t>1766758</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3279957</t>
+          <t>3284353</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3452672</t>
+          <t>3452218</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>50,04%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1099171</t>
+          <t>1105759</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1211791</t>
+          <t>1216823</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1144142</t>
+          <t>1149112</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1262227</t>
+          <t>1262323</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2279351</t>
+          <t>2279476</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2452819</t>
+          <t>2444088</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8900,7 +8900,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,43%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>426280</t>
+          <t>428905</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>509524</t>
+          <t>510399</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>463313</t>
+          <t>462958</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>550939</t>
+          <t>549834</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>919064</t>
+          <t>918058</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1037744</t>
+          <t>1035657</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,01%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>57464</t>
+          <t>55308</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>93095</t>
+          <t>89713</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>72129</t>
+          <t>71252</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>110918</t>
+          <t>110145</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>135941</t>
+          <t>138477</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>188403</t>
+          <t>188872</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10935</t>
+          <t>10121</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>28438</t>
+          <t>27828</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10879</t>
+          <t>11041</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>29559</t>
+          <t>30009</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9204,7 +9204,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>26006</t>
+          <t>25561</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>51360</t>
+          <t>51216</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -9605,32 +9605,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>255513</t>
+          <t>281432</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>234197</t>
+          <t>258967</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>275812</t>
+          <t>305399</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9640,32 +9640,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>336756</t>
+          <t>355072</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>314451</t>
+          <t>332583</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>359174</t>
+          <t>376601</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9675,32 +9675,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>592269</t>
+          <t>636504</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>562031</t>
+          <t>606932</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>623574</t>
+          <t>670471</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>48,26%</t>
         </is>
       </c>
     </row>
@@ -9718,32 +9718,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>133548</t>
+          <t>150927</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>116399</t>
+          <t>132695</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>153418</t>
+          <t>171287</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9753,32 +9753,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>228941</t>
+          <t>257332</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>209831</t>
+          <t>236294</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>248115</t>
+          <t>279786</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9788,32 +9788,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>362490</t>
+          <t>408258</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>334349</t>
+          <t>376724</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>389852</t>
+          <t>436301</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>31,4%</t>
         </is>
       </c>
     </row>
@@ -9831,32 +9831,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>76728</t>
+          <t>90572</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>63117</t>
+          <t>74407</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>93045</t>
+          <t>109698</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9866,32 +9866,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>111783</t>
+          <t>122387</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>98463</t>
+          <t>108235</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>125753</t>
+          <t>138439</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9901,32 +9901,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>188511</t>
+          <t>212960</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>166888</t>
+          <t>191917</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>208900</t>
+          <t>237741</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -9944,32 +9944,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31378</t>
+          <t>35428</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23592</t>
+          <t>26096</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42564</t>
+          <t>47519</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9979,32 +9979,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>57859</t>
+          <t>63883</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47944</t>
+          <t>51742</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70393</t>
+          <t>76014</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10014,32 +10014,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>89237</t>
+          <t>99311</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>75606</t>
+          <t>84871</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>104915</t>
+          <t>117495</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -10057,32 +10057,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>13469</t>
+          <t>15384</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8045</t>
+          <t>8922</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20810</t>
+          <t>23336</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10092,32 +10092,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>14182</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9906</t>
+          <t>11604</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>20686</t>
+          <t>24393</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10127,32 +10127,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>27651</t>
+          <t>32266</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20275</t>
+          <t>24518</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>36835</t>
+          <t>43782</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -10170,17 +10170,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>510636</t>
+          <t>573743</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>510636</t>
+          <t>573743</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>510636</t>
+          <t>573743</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10205,17 +10205,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>749522</t>
+          <t>815556</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>749522</t>
+          <t>815556</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>749522</t>
+          <t>815556</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10240,17 +10240,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1260158</t>
+          <t>1389299</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1260158</t>
+          <t>1389299</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1260158</t>
+          <t>1389299</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10287,32 +10287,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1444513</t>
+          <t>1265859</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1324529</t>
+          <t>1212757</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1723729</t>
+          <t>1321999</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10322,32 +10322,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1194020</t>
+          <t>1215839</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>913538</t>
+          <t>1175120</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1337256</t>
+          <t>1258785</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10357,32 +10357,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2638533</t>
+          <t>2481698</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2313489</t>
+          <t>2413954</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2923369</t>
+          <t>2546310</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>57,93%</t>
         </is>
       </c>
     </row>
@@ -10400,32 +10400,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>621450</t>
+          <t>704535</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>405205</t>
+          <t>653956</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>713471</t>
+          <t>755427</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10435,32 +10435,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>820087</t>
+          <t>694112</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>660910</t>
+          <t>655649</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1187174</t>
+          <t>735744</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10470,32 +10470,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1441537</t>
+          <t>1398647</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1207295</t>
+          <t>1335865</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1923250</t>
+          <t>1459530</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>33,2%</t>
         </is>
       </c>
     </row>
@@ -10513,32 +10513,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>145710</t>
+          <t>164523</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>104172</t>
+          <t>138772</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>179070</t>
+          <t>194126</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10548,32 +10548,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>134967</t>
+          <t>153362</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>97389</t>
+          <t>133239</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>160236</t>
+          <t>174971</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10583,32 +10583,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>280677</t>
+          <t>317884</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>225655</t>
+          <t>286015</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>325087</t>
+          <t>350497</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -10626,32 +10626,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>55201</t>
+          <t>70715</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37387</t>
+          <t>56200</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74137</t>
+          <t>92601</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10661,32 +10661,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>67801</t>
+          <t>78316</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48277</t>
+          <t>62380</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85647</t>
+          <t>97060</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10696,32 +10696,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>123003</t>
+          <t>149031</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>95947</t>
+          <t>125898</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>149819</t>
+          <t>174293</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -10739,32 +10739,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>21188</t>
+          <t>22791</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12181</t>
+          <t>14277</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33343</t>
+          <t>35176</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10774,67 +10774,67 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>17931</t>
+          <t>25818</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11115</t>
+          <t>17538</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31198</t>
+          <t>38570</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>48609</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>35014</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>64904</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>0,8%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>39119</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>26543</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>54309</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -10852,17 +10852,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2288062</t>
+          <t>2228423</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2288062</t>
+          <t>2228423</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2288062</t>
+          <t>2228423</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10887,17 +10887,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2234806</t>
+          <t>2167447</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2234806</t>
+          <t>2167447</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2234806</t>
+          <t>2167447</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10922,17 +10922,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4522869</t>
+          <t>4395870</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4522869</t>
+          <t>4395870</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4522869</t>
+          <t>4395870</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10969,32 +10969,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>413924</t>
+          <t>452504</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>387521</t>
+          <t>425146</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>437829</t>
+          <t>479647</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11004,32 +11004,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>467332</t>
+          <t>517898</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>446111</t>
+          <t>497623</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>486508</t>
+          <t>539941</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11039,32 +11039,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>881256</t>
+          <t>970401</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>848982</t>
+          <t>936117</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>913349</t>
+          <t>1005208</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>69,65%</t>
         </is>
       </c>
     </row>
@@ -11082,32 +11082,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>183032</t>
+          <t>202013</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>159503</t>
+          <t>177230</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>206717</t>
+          <t>226929</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11117,32 +11117,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>152504</t>
+          <t>169976</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>135059</t>
+          <t>151803</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>171721</t>
+          <t>190633</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11152,32 +11152,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>335535</t>
+          <t>371989</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>305843</t>
+          <t>339742</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>367962</t>
+          <t>402790</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>27,91%</t>
         </is>
       </c>
     </row>
@@ -11195,32 +11195,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>34169</t>
+          <t>37236</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23494</t>
+          <t>26375</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>49583</t>
+          <t>55465</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11230,32 +11230,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>28491</t>
+          <t>32894</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20403</t>
+          <t>23788</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40288</t>
+          <t>44668</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11265,32 +11265,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>62659</t>
+          <t>70130</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>48410</t>
+          <t>55331</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>80624</t>
+          <t>88613</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -11308,69 +11308,69 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9998</t>
+          <t>12648</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5726</t>
+          <t>7023</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17437</t>
+          <t>21181</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2,98%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>6613</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>3280</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>11400</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
           <t>1,55%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>5081</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>2422</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>9063</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>25</t>
@@ -11378,32 +11378,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>15079</t>
+          <t>19261</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9858</t>
+          <t>12951</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23139</t>
+          <t>28159</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -11421,32 +11421,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>5430</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>1545</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10391</t>
+          <t>13491</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11456,32 +11456,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5646</t>
+          <t>6011</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2564</t>
+          <t>2818</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10693</t>
+          <t>11653</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11491,32 +11491,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>9366</t>
+          <t>11442</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5197</t>
+          <t>6422</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16970</t>
+          <t>20846</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -11534,17 +11534,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>644842</t>
+          <t>709831</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>644842</t>
+          <t>709831</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>644842</t>
+          <t>709831</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11569,17 +11569,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>659054</t>
+          <t>733391</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>659054</t>
+          <t>733391</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>659054</t>
+          <t>733391</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11604,17 +11604,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1303896</t>
+          <t>1443222</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1303896</t>
+          <t>1443222</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1303896</t>
+          <t>1443222</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11651,32 +11651,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2113950</t>
+          <t>1999794</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1987432</t>
+          <t>1935854</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2404777</t>
+          <t>2066129</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11686,32 +11686,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1998108</t>
+          <t>2088809</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1613122</t>
+          <t>2035133</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2143271</t>
+          <t>2145033</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11721,32 +11721,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>4112059</t>
+          <t>4088603</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3741887</t>
+          <t>4014617</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4374408</t>
+          <t>4172102</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>57,72%</t>
         </is>
       </c>
     </row>
@@ -11764,32 +11764,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>938030</t>
+          <t>1057474</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>740003</t>
+          <t>999297</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1031808</t>
+          <t>1115840</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11799,32 +11799,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1201532</t>
+          <t>1121419</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1039282</t>
+          <t>1075091</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1726856</t>
+          <t>1174332</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11834,32 +11834,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2139562</t>
+          <t>2178893</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1924562</t>
+          <t>2108624</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2704059</t>
+          <t>2247604</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>31,09%</t>
         </is>
       </c>
     </row>
@@ -11877,32 +11877,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>256606</t>
+          <t>292331</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>194457</t>
+          <t>258401</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>294580</t>
+          <t>326832</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11912,32 +11912,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>275241</t>
+          <t>308643</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>222655</t>
+          <t>280798</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>306972</t>
+          <t>332920</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11947,32 +11947,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>531848</t>
+          <t>600974</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>466711</t>
+          <t>551768</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>590926</t>
+          <t>645121</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -11990,32 +11990,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>96578</t>
+          <t>118792</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>72932</t>
+          <t>97885</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>118814</t>
+          <t>142575</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12025,32 +12025,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>130741</t>
+          <t>148811</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>105036</t>
+          <t>128012</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>153515</t>
+          <t>170618</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12060,32 +12060,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>227319</t>
+          <t>267603</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>193934</t>
+          <t>237168</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>259900</t>
+          <t>301388</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -12103,32 +12103,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>38376</t>
+          <t>43605</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>26370</t>
+          <t>31708</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>52113</t>
+          <t>60344</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12138,67 +12138,67 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>37759</t>
+          <t>48712</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>28575</t>
+          <t>37334</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>51105</t>
+          <t>64799</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>92317</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>75385</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>111833</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>1,04%</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>76135</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>60930</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>96370</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -12216,17 +12216,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3443540</t>
+          <t>3511996</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3443540</t>
+          <t>3511996</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3443540</t>
+          <t>3511996</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12251,17 +12251,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3643382</t>
+          <t>3716394</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3643382</t>
+          <t>3716394</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3643382</t>
+          <t>3716394</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12286,17 +12286,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7086922</t>
+          <t>7228390</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7086922</t>
+          <t>7228390</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7086922</t>
+          <t>7228390</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
